--- a/AC_2014/3-Karimnagar_7_26_Karimnagar.xlsx
+++ b/AC_2014/3-Karimnagar_7_26_Karimnagar.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -734,7 +770,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4475</v>
+        <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>222</v>
@@ -770,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>4956</v>
+        <v>481</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>0</v>
@@ -779,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>4958</v>
+        <v>483</v>
       </c>
       <c r="S7" s="6" t="n">
         <v>0</v>
@@ -22302,224 +22338,225 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="7" t="inlineStr">
+      <c r="A344" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B344" s="8" t="inlineStr"/>
-      <c r="C344" s="9">
+      <c r="B344" s="11" t="inlineStr"/>
+      <c r="C344" s="19">
         <f>SUM(C6:C343)</f>
         <v/>
       </c>
-      <c r="D344" s="9">
+      <c r="D344" s="19">
         <f>SUM(D6:D343)</f>
         <v/>
       </c>
-      <c r="E344" s="9">
+      <c r="E344" s="19">
         <f>SUM(E6:E343)</f>
         <v/>
       </c>
-      <c r="F344" s="9">
+      <c r="F344" s="19">
         <f>SUM(F6:F343)</f>
         <v/>
       </c>
-      <c r="G344" s="9">
+      <c r="G344" s="19">
         <f>SUM(G6:G343)</f>
         <v/>
       </c>
-      <c r="H344" s="9">
+      <c r="H344" s="19">
         <f>SUM(H6:H343)</f>
         <v/>
       </c>
-      <c r="I344" s="9">
+      <c r="I344" s="19">
         <f>SUM(I6:I343)</f>
         <v/>
       </c>
-      <c r="J344" s="9">
+      <c r="J344" s="19">
         <f>SUM(J6:J343)</f>
         <v/>
       </c>
-      <c r="K344" s="9">
+      <c r="K344" s="19">
         <f>SUM(K6:K343)</f>
         <v/>
       </c>
-      <c r="L344" s="9">
+      <c r="L344" s="19">
         <f>SUM(L6:L343)</f>
         <v/>
       </c>
-      <c r="M344" s="9">
+      <c r="M344" s="19">
         <f>SUM(M6:M343)</f>
         <v/>
       </c>
-      <c r="N344" s="9">
+      <c r="N344" s="19">
         <f>SUM(N6:N343)</f>
         <v/>
       </c>
-      <c r="O344" s="9">
+      <c r="O344" s="19">
         <f>SUM(O6:O343)</f>
         <v/>
       </c>
-      <c r="P344" s="9">
+      <c r="P344" s="19">
         <f>SUM(P6:P343)</f>
         <v/>
       </c>
-      <c r="Q344" s="9">
+      <c r="Q344" s="19">
         <f>SUM(Q6:Q343)</f>
         <v/>
       </c>
-      <c r="R344" s="9">
+      <c r="R344" s="19">
         <f>SUM(R6:R343)</f>
         <v/>
       </c>
-      <c r="S344" s="9">
+      <c r="S344" s="19">
         <f>SUM(S6:S343)</f>
         <v/>
       </c>
-      <c r="T344" s="9">
+      <c r="T344" s="19">
         <f>SUM(T6:T343)</f>
         <v/>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="10" t="inlineStr">
+      <c r="A345" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B345" s="11" t="inlineStr"/>
-      <c r="C345" s="12" t="n">
+      <c r="C345" s="19" t="n">
         <v>963</v>
       </c>
-      <c r="D345" s="12" t="n">
+      <c r="D345" s="19" t="n">
         <v>675</v>
       </c>
-      <c r="E345" s="12" t="n">
+      <c r="E345" s="19" t="n">
         <v>763</v>
       </c>
-      <c r="F345" s="12" t="n">
+      <c r="F345" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G345" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I345" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K345" s="12" t="n">
+      <c r="G345" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K345" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O345" s="12" t="n">
+      <c r="L345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O345" s="19" t="n">
         <v>2419</v>
       </c>
-      <c r="P345" s="12" t="n">
+      <c r="P345" s="19" t="n">
         <v>444</v>
       </c>
-      <c r="Q345" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R345" s="12" t="n">
+      <c r="Q345" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R345" s="19" t="n">
         <v>2865</v>
       </c>
-      <c r="S345" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T345" s="13" t="n">
+      <c r="S345" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T345" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="14" t="inlineStr">
+      <c r="A346" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B346" s="15" t="inlineStr"/>
-      <c r="C346" s="16">
+      <c r="B346" s="11" t="inlineStr"/>
+      <c r="C346" s="20">
         <f>C344+C345</f>
         <v/>
       </c>
-      <c r="D346" s="16">
+      <c r="D346" s="20">
         <f>D344+D345</f>
         <v/>
       </c>
-      <c r="E346" s="16">
+      <c r="E346" s="20">
         <f>E344+E345</f>
         <v/>
       </c>
-      <c r="F346" s="16">
+      <c r="F346" s="20">
         <f>F344+F345</f>
         <v/>
       </c>
-      <c r="G346" s="16">
+      <c r="G346" s="20">
         <f>G344+G345</f>
         <v/>
       </c>
-      <c r="H346" s="16">
+      <c r="H346" s="20">
         <f>H344+H345</f>
         <v/>
       </c>
-      <c r="I346" s="16">
+      <c r="I346" s="20">
         <f>I344+I345</f>
         <v/>
       </c>
-      <c r="J346" s="16">
+      <c r="J346" s="20">
         <f>J344+J345</f>
         <v/>
       </c>
-      <c r="K346" s="16">
+      <c r="K346" s="20">
         <f>K344+K345</f>
         <v/>
       </c>
-      <c r="L346" s="16">
+      <c r="L346" s="20">
         <f>L344+L345</f>
         <v/>
       </c>
-      <c r="M346" s="16">
+      <c r="M346" s="20">
         <f>M344+M345</f>
         <v/>
       </c>
-      <c r="N346" s="16">
+      <c r="N346" s="20">
         <f>N344+N345</f>
         <v/>
       </c>
-      <c r="O346" s="16">
+      <c r="O346" s="20">
         <f>O344+O345</f>
         <v/>
       </c>
-      <c r="P346" s="16">
+      <c r="P346" s="20">
         <f>P344+P345</f>
         <v/>
       </c>
-      <c r="Q346" s="16">
+      <c r="Q346" s="20">
         <f>Q344+Q345</f>
         <v/>
       </c>
-      <c r="R346" s="16">
+      <c r="R346" s="20">
         <f>R344+R345</f>
         <v/>
       </c>
-      <c r="S346" s="16">
+      <c r="S346" s="20">
         <f>S344+S345</f>
         <v/>
       </c>
-      <c r="T346" s="17" t="n">
-        <v>0</v>
+      <c r="T346" s="20">
+        <f>T344+T345</f>
+        <v/>
       </c>
     </row>
   </sheetData>
